--- a/data/TTN/最新版班表/TTN_TA.xlsx
+++ b/data/TTN/最新版班表/TTN_TA.xlsx
@@ -3180,9 +3180,9 @@
       </c>
       <c r="AB17" s="1" t="inlineStr">
         <is>
-          <t>13:21
-NH2511
-21:21
+          <t>12:16
+NF0503
+20:16
 8:00</t>
         </is>
       </c>
@@ -4244,9 +4244,12 @@
 8:27</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD22" s="1" t="inlineStr">
+        <is>
+          <t>5:26
+NF2001
+13:26
+8:00</t>
         </is>
       </c>
     </row>
@@ -4452,11 +4455,8 @@
       </c>
       <c r="AD23" s="1" t="inlineStr">
         <is>
-          <t>5:26
-DO3W
-NF2001
-13:26
-8:00</t>
+          <t>DO3W
+DO3X</t>
         </is>
       </c>
     </row>
@@ -8872,12 +8872,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="AB44" s="1" t="inlineStr">
-        <is>
-          <t>7:34
-NH0019
-16:16
-8:42</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AC44" s="1" t="inlineStr">
@@ -11480,8 +11477,16 @@
           <t>NH6511</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>NG6511</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NF6036</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>DO1</t>
@@ -11585,10 +11590,10 @@
       </c>
       <c r="AB57" s="1" t="inlineStr">
         <is>
-          <t>12:16
-NF0503
-20:16
-8:00</t>
+          <t>7:34
+NH0019
+16:16
+8:42</t>
         </is>
       </c>
       <c r="AC57" s="1" t="inlineStr">
@@ -22440,9 +22445,12 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AB108" s="1" t="inlineStr">
+        <is>
+          <t>13:21
+NH2511
+21:21
+8:00</t>
         </is>
       </c>
       <c r="AC108" s="1" t="inlineStr">
@@ -31151,9 +31159,21 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>NG6001</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>NF6011</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>NF6013</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
@@ -31315,9 +31335,21 @@
           <t>NF6001</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>NF6004</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>NF6007</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>NG6001</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
@@ -31483,13 +31515,21 @@
           <t>NF6020</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>NF6011</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>DO1</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>NG6018</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -31651,8 +31691,16 @@
           <t>NG6548</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>NG6543</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>NG6549</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t>DO1</t>
@@ -31818,13 +31866,21 @@
           <t>NF6005</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>NG6020</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>DO1</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>NF6002</t>
+        </is>
+      </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
@@ -32063,8 +32119,16 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>NG6001</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>NF6005</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
@@ -32230,8 +32294,16 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>NF6543</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>NG6536</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
@@ -32578,8 +32650,16 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>NF6002</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>NF6012</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
@@ -32741,13 +32821,21 @@
           <t>NG6023</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>NF6002</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>DO1</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>NF6543</t>
+        </is>
+      </c>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr">

--- a/data/TTN/最新版班表/TTN_TA.xlsx
+++ b/data/TTN/最新版班表/TTN_TA.xlsx
@@ -1369,7 +1369,7 @@
       <c r="N9" s="1" t="inlineStr">
         <is>
           <t>15:49
-NH2540
+NF2540
 23:56
 8:07</t>
         </is>
@@ -1812,10 +1812,10 @@
       </c>
       <c r="P11" s="1" t="inlineStr">
         <is>
-          <t>6:36
-NG2011
-14:36
-8:00</t>
+          <t>7:31
+NG1019
+16:16
+8:45</t>
         </is>
       </c>
       <c r="Q11" s="1" t="inlineStr">
@@ -2639,22 +2639,22 @@
       <c r="L15" s="1" t="inlineStr">
         <is>
           <t>6:51
-NH0013
+NG0013
 14:51
 8:00</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
-        <is>
-          <t>6:10
-NF0007
-14:10
-8:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>7:24
+NF0018
+15:24
+8:00</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -3071,17 +3071,17 @@
 8:22</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N17" s="1" t="inlineStr">
-        <is>
-          <t>7:24
-NF0018
-15:24
-8:00</t>
+      <c r="M17" s="1" t="inlineStr">
+        <is>
+          <t>6:10
+NF0007
+14:10
+8:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -3305,18 +3305,15 @@
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
-          <t>7:31
-NG1019
-16:16
-8:45</t>
-        </is>
-      </c>
-      <c r="Q18" s="1" t="inlineStr">
-        <is>
-          <t>6:31
-NG3009
-14:31
-8:00</t>
+          <t>6:36
+NG2011
+14:36
+8:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr">
@@ -3327,14 +3324,20 @@
 8:00</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S18" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="T18" s="1" t="inlineStr">
+        <is>
+          <t>7:01
+NH0014
+15:11
+8:10</t>
         </is>
       </c>
       <c r="U18" s="1" t="inlineStr">
@@ -3350,12 +3353,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="W18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X18" s="1" t="inlineStr">
@@ -4158,23 +4158,23 @@
       </c>
       <c r="R22" s="1" t="inlineStr">
         <is>
-          <t>7:01
-NH0014
-15:11
-8:10</t>
-        </is>
-      </c>
-      <c r="S22" s="1" t="inlineStr">
-        <is>
-          <t>16:24
-NH0545
-24:26
-8:02</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+          <t>6:36
+NG0011
+14:36
+8:00</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="T22" s="1" t="inlineStr">
+        <is>
+          <t>6:10
+NG0007
+14:10
+8:00</t>
         </is>
       </c>
       <c r="U22" s="1" t="inlineStr">
@@ -4215,17 +4215,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z22" s="1" t="inlineStr">
-        <is>
-          <t>7:24
-NF0018
-15:24
-8:00</t>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>DO1</t>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB22" s="1" t="inlineStr">
@@ -4424,9 +4421,12 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z23" s="1" t="inlineStr">
+        <is>
+          <t>7:24
+NF0018
+15:24
+8:00</t>
         </is>
       </c>
       <c r="AA23" s="1" t="inlineStr">
@@ -5200,12 +5200,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="O27" s="1" t="inlineStr">
-        <is>
-          <t>15:24
-NG0531
-23:26
-8:02</t>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>MLP</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr">
@@ -6085,10 +6082,10 @@
       </c>
       <c r="R31" s="1" t="inlineStr">
         <is>
-          <t>16:34
-NF0549
-24:38
-8:04</t>
+          <t>14:41
+NF0526
+22:41
+8:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="inlineStr">
@@ -6677,7 +6674,7 @@
       <c r="K34" s="1" t="inlineStr">
         <is>
           <t>12:11
-NH1501
+NG1501
 20:11
 8:00</t>
         </is>
@@ -7797,10 +7794,10 @@
       </c>
       <c r="U39" s="1" t="inlineStr">
         <is>
-          <t>6:46
-NF5901
-16:46
-10:00</t>
+          <t>5:26
+NG0002
+15:01
+9:35</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -7978,10 +7975,10 @@
       </c>
       <c r="Q40" s="1" t="inlineStr">
         <is>
-          <t>13:49
-NF0516
-21:51
-8:02</t>
+          <t>14:39
+NF2526
+22:51
+8:12</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -8007,10 +8004,10 @@
       </c>
       <c r="U40" s="1" t="inlineStr">
         <is>
-          <t>14:04
-NF5906
-22:06
-8:02</t>
+          <t>9:04
+NF0027
+17:11
+8:07</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -8792,18 +8789,18 @@
       </c>
       <c r="Q44" s="1" t="inlineStr">
         <is>
-          <t>14:39
-NF2526
-22:51
-8:12</t>
+          <t>13:49
+NF0516
+21:51
+8:02</t>
         </is>
       </c>
       <c r="R44" s="1" t="inlineStr">
         <is>
-          <t>11:36
-NF0034
-19:36
-8:00</t>
+          <t>9:24
+NF0029
+18:36
+9:12</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -8821,11 +8818,11 @@
       </c>
       <c r="U44" s="1" t="inlineStr">
         <is>
-          <t>9:04
+          <t>14:04
 DO3W
-NF0027
-17:11
-8:07</t>
+NF5906
+22:06
+8:02</t>
         </is>
       </c>
       <c r="V44" s="1" t="inlineStr">
@@ -8867,9 +8864,12 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AA44" s="1" t="inlineStr">
+        <is>
+          <t>13:21
+NG0511
+21:21
+8:00</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -8977,12 +8977,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M45" s="1" t="inlineStr">
-        <is>
-          <t>7:49
-NF0020
-16:11
-8:22</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>MLP</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -9433,9 +9430,12 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q47" s="1" t="inlineStr">
+        <is>
+          <t>6:31
+NG3009
+14:31
+8:00</t>
         </is>
       </c>
       <c r="R47" s="1" t="inlineStr">
@@ -9454,12 +9454,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="T47" s="1" t="inlineStr">
-        <is>
-          <t>7:01
-NH0014
-15:11
-8:10</t>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -9633,10 +9630,10 @@
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>14:41
-NG1526
-22:41
-8:00</t>
+          <t>13:14
+NF0508
+21:16
+8:02</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr">
@@ -11350,10 +11347,10 @@
       </c>
       <c r="U56" s="1" t="inlineStr">
         <is>
-          <t>5:26
-NG0002
-15:01
-9:35</t>
+          <t>6:46
+NF5901
+16:46
+10:00</t>
         </is>
       </c>
       <c r="V56" s="1" t="inlineStr">
@@ -11938,10 +11935,10 @@
       </c>
       <c r="R59" s="1" t="inlineStr">
         <is>
-          <t>6:36
-NG0011
-14:36
-8:00</t>
+          <t>7:01
+NH0014
+15:11
+8:10</t>
         </is>
       </c>
       <c r="S59" s="1" t="inlineStr">
@@ -12979,7 +12976,7 @@
       <c r="O64" s="1" t="inlineStr">
         <is>
           <t>14:41
-NH1526
+NG1526
 22:41
 8:00</t>
         </is>
@@ -13177,9 +13174,9 @@
       </c>
       <c r="L65" s="1" t="inlineStr">
         <is>
-          <t>14:41
-NG0526
-22:41
+          <t>11:46
+NG0038
+19:46
 8:00</t>
         </is>
       </c>
@@ -13391,18 +13388,15 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="N66" s="1" t="inlineStr">
-        <is>
-          <t>15:49
-NF2540
-23:56
-8:07</t>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>MLP</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
           <t>15:24
-NH0531
+NG0531
 23:26
 8:02</t>
         </is>
@@ -13848,9 +13842,9 @@
       </c>
       <c r="P68" s="1" t="inlineStr">
         <is>
-          <t>12:36
-NF3506
-20:36
+          <t>13:16
+NF1508
+21:16
 8:00</t>
         </is>
       </c>
@@ -15766,12 +15760,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P77" s="1" t="inlineStr">
-        <is>
-          <t>5:46
-NG1004
-13:46
-8:00</t>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>MLP</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -16154,17 +16145,17 @@
       </c>
       <c r="K79" s="1" t="inlineStr">
         <is>
-          <t>12:11
-NG1501
-20:11
+          <t>13:16
+PAY1
+21:16
 8:00</t>
         </is>
       </c>
       <c r="L79" s="1" t="inlineStr">
         <is>
-          <t>11:46
-NG0038
-19:46
+          <t>13:16
+PAY1
+21:16
 8:00</t>
         </is>
       </c>
@@ -16180,10 +16171,10 @@
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>13:14
-NF0508
+          <t>13:16
+PAY1
 21:16
-8:02</t>
+8:00</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr">
@@ -16201,17 +16192,17 @@
       </c>
       <c r="R79" s="1" t="inlineStr">
         <is>
-          <t>9:24
-NF0029
-18:36
-9:12</t>
+          <t>11:36
+NF0034
+19:36
+8:00</t>
         </is>
       </c>
       <c r="S79" s="1" t="inlineStr">
         <is>
-          <t>11:46
-NH0038
-19:46
+          <t>14:41
+NG0526
+22:41
 8:00</t>
         </is>
       </c>
@@ -16620,7 +16611,7 @@
       <c r="P81" s="1" t="inlineStr">
         <is>
           <t>5:46
-NH1004
+NG1004
 13:46
 8:00</t>
         </is>
@@ -17233,12 +17224,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L84" s="1" t="inlineStr">
-        <is>
-          <t>7:49
-NH0020
-16:11
-8:22</t>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NHS1</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -18910,9 +18898,9 @@
       </c>
       <c r="K92" s="1" t="inlineStr">
         <is>
-          <t>14:16
-NF0521
-22:16
+          <t>13:16
+PAY1
+21:16
 8:00</t>
         </is>
       </c>
@@ -18955,10 +18943,10 @@
       </c>
       <c r="Q92" s="1" t="inlineStr">
         <is>
-          <t>12:14
-NF0504
-20:26
-8:12</t>
+          <t>13:39
+NG2518
+22:11
+8:32</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -19124,18 +19112,15 @@
       </c>
       <c r="K93" s="1" t="inlineStr">
         <is>
-          <t>13:16
-PAY1
-21:16
-8:00</t>
-        </is>
-      </c>
-      <c r="L93" s="1" t="inlineStr">
-        <is>
-          <t>6:51
-NG0013
-14:51
-8:00</t>
+          <t>8:30
+CMP
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>MLP</t>
         </is>
       </c>
       <c r="M93" s="1" t="inlineStr">
@@ -20880,10 +20865,10 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>14:41
-NF0526
-22:41
-8:00</t>
+          <t>16:34
+NF0549
+24:38
+8:04</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -21974,10 +21959,10 @@
       </c>
       <c r="W106" s="1" t="inlineStr">
         <is>
-          <t>7:01
-NF2014
-15:16
-8:15</t>
+          <t>9:01
+NG2027
+17:36
+8:35</t>
         </is>
       </c>
       <c r="X106" s="1" t="inlineStr">
@@ -22108,9 +22093,9 @@
       </c>
       <c r="L107" s="1" t="inlineStr">
         <is>
-          <t>13:21
-NG0511
-21:21
+          <t>14:41
+NG0526
+22:41
 8:00</t>
         </is>
       </c>
@@ -22137,9 +22122,9 @@
       </c>
       <c r="P107" s="1" t="inlineStr">
         <is>
-          <t>11:11
-NF1033
-19:11
+          <t>15:11
+NH2529
+23:11
 8:00</t>
         </is>
       </c>
@@ -22334,9 +22319,9 @@
       </c>
       <c r="M108" s="1" t="inlineStr">
         <is>
-          <t>12:36
-NG0506
-20:36
+          <t>14:41
+NF0526
+22:41
 8:00</t>
         </is>
       </c>
@@ -22437,12 +22422,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA108" s="1" t="inlineStr">
-        <is>
-          <t>13:21
-NG0511
-21:21
-8:00</t>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB108" s="1" t="inlineStr">
@@ -22535,7 +22517,7 @@
       <c r="J109" s="1" t="inlineStr">
         <is>
           <t>9:30
-I309A
+I308A
 17:30
 8:00</t>
         </is>
@@ -22572,7 +22554,7 @@
       <c r="O109" s="1" t="inlineStr">
         <is>
           <t>9:30
-I309A
+I308A
 17:30
 8:00</t>
         </is>
@@ -22765,9 +22747,9 @@
       </c>
       <c r="M110" s="1" t="inlineStr">
         <is>
-          <t>14:41
-NF0526
-22:41
+          <t>12:36
+NG0506
+20:36
 8:00</t>
         </is>
       </c>
@@ -23021,7 +23003,7 @@
       <c r="R111" s="1" t="inlineStr">
         <is>
           <t>15:31
-NH0536
+NF0536
 23:31
 8:00</t>
         </is>
@@ -23055,10 +23037,10 @@
       </c>
       <c r="W111" s="1" t="inlineStr">
         <is>
-          <t>9:01
-NG2027
-17:36
-8:35</t>
+          <t>7:01
+NF2014
+15:16
+8:15</t>
         </is>
       </c>
       <c r="X111" s="1" t="inlineStr">
@@ -23238,9 +23220,9 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>15:31
-NF0536
-23:31
+          <t>12:36
+NH0506
+20:36
 8:00</t>
         </is>
       </c>
@@ -24114,7 +24096,7 @@
       <c r="S116" s="1" t="inlineStr">
         <is>
           <t>11:16
-NH0036
+NF0036
 19:16
 8:00</t>
         </is>
@@ -24708,9 +24690,9 @@
       </c>
       <c r="L119" s="1" t="inlineStr">
         <is>
-          <t>15:11
-NH0529
-23:11
+          <t>15:31
+NF0536
+23:31
 8:00</t>
         </is>
       </c>
@@ -24920,10 +24902,10 @@
       </c>
       <c r="K120" s="1" t="inlineStr">
         <is>
-          <t>14:34
-NH0543
-24:16
-9:42</t>
+          <t>14:16
+NF0521
+22:16
+8:00</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -26060,9 +26042,9 @@
       </c>
       <c r="S125" s="1" t="inlineStr">
         <is>
-          <t>14:41
-NG0526
-22:41
+          <t>11:46
+NH0038
+19:46
 8:00</t>
         </is>
       </c>
@@ -27742,7 +27724,7 @@
       <c r="M133" s="1" t="inlineStr">
         <is>
           <t>7:49
-NG0020
+NF0020
 16:11
 8:22</t>
         </is>
@@ -27998,17 +27980,17 @@
 8:00</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T134" s="1" t="inlineStr">
-        <is>
-          <t>6:10
-NG0007
-14:10
-8:00</t>
+      <c r="S134" s="1" t="inlineStr">
+        <is>
+          <t>16:24
+NH0545
+24:26
+8:02</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="U134" s="1" t="inlineStr">
@@ -28633,10 +28615,10 @@
       </c>
       <c r="Q137" s="1" t="inlineStr">
         <is>
-          <t>13:39
-NG2518
-22:11
-8:32</t>
+          <t>12:14
+NF0504
+20:26
+8:12</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -29713,9 +29695,9 @@
       </c>
       <c r="P142" s="1" t="inlineStr">
         <is>
-          <t>15:11
-NH2529
-23:11
+          <t>11:11
+NF1033
+19:11
 8:00</t>
         </is>
       </c>
@@ -30320,9 +30302,9 @@
       </c>
       <c r="L145" s="1" t="inlineStr">
         <is>
-          <t>15:31
-NF0536
-23:31
+          <t>13:21
+NG0511
+21:21
 8:00</t>
         </is>
       </c>
@@ -30346,9 +30328,9 @@
       </c>
       <c r="P145" s="1" t="inlineStr">
         <is>
-          <t>13:16
-NF1508
-21:16
+          <t>12:36
+NF3506
+20:36
 8:00</t>
         </is>
       </c>
@@ -31174,8 +31156,16 @@
           <t>NF6013</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>NF6002</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>NF6005</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>DO3X</t>
@@ -31350,7 +31340,11 @@
           <t>NG6001</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>NF6005</t>
+        </is>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>DO1</t>
@@ -31530,8 +31524,16 @@
           <t>NG6018</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>NF6013</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>NG6002</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>DO3X</t>
@@ -31706,8 +31708,16 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>NG6545</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>NG6511</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>DO3X</t>
@@ -31881,8 +31891,16 @@
           <t>NF6002</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>NG6018</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>NF6001</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>DO3X</t>
@@ -32129,8 +32147,16 @@
           <t>NF6005</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>NF6007</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>NF6009</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>DO3X</t>
@@ -32304,8 +32330,16 @@
           <t>NG6536</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>NG6547</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>NF6514</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>DO3X</t>
@@ -32483,13 +32517,19 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>NG6549</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>NG6514</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>NG6541</t>
         </is>
       </c>
       <c r="Q158" s="1" t="inlineStr">
@@ -32660,8 +32700,16 @@
           <t>NF6012</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>NF6009</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>NF6011</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>DO3X</t>
@@ -32836,8 +32884,16 @@
           <t>NF6543</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>NG6536</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>NF6521</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>DO3X</t>
